--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_306_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_306_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
         <v>9</v>
@@ -3239,16 +3239,16 @@
         <v>93</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X27" t="n">
         <v>22</v>
@@ -4488,16 +4488,16 @@
         <v>17</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6196,16 +6196,16 @@
         <v>90</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_306_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_306_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
         <v>16</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>4</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,14 +2915,14 @@
         <v>3</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3251,14 +3251,14 @@
         <v>10</v>
       </c>
       <c r="X27" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3912,14 +3912,14 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA33" t="n">
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6208,14 +6208,14 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
